--- a/input/16cut_hot_AB.xlsx
+++ b/input/16cut_hot_AB.xlsx
@@ -1804,6 +1804,36 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="46" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1811,30 +1841,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1843,11 +1849,11 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="46" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -1858,11 +1864,38 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="8">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="8">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="8">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="8">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="8">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="8">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="23">
       <alignment horizontal="center" vertical="center"/>
@@ -1909,40 +1942,22 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="8">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="8">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="8">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="8">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="8">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="8">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="57">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="56">
@@ -1954,145 +1969,136 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="56">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="57">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="36" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="37" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="40" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="39" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="41" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="43" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="44" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="45" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="45" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="43" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="44" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="39" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="40" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="37" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="41" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="36" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="45" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="43" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="44" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="45" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="43" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="44" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="36">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="36">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="18">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="18">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="23">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="23">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="30">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="30">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="40">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="40">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="40">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="40">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="40">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="40">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="40">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="40">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="40">
@@ -2101,73 +2107,67 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="36">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="36">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="30">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="30">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="18">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="18">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="23">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="40">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="40">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="40">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="40">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="40">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="23">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="36">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="30">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="18">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="23">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -2630,7 +2630,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="15.75" customHeight="1">
-      <c r="A1" s="316" t="inlineStr">
+      <c r="A1" s="318" t="inlineStr">
         <is>
           <t>16 граней горячая фиксация АВ</t>
         </is>
@@ -2687,26 +2687,26 @@
       </c>
     </row>
     <row r="3" ht="16.5" customHeight="1" thickBot="1" thickTop="1">
-      <c r="A3" s="303" t="inlineStr">
+      <c r="A3" s="310" t="inlineStr">
         <is>
           <t>JET BLACK AB</t>
         </is>
       </c>
-      <c r="B3" s="303" t="inlineStr">
+      <c r="B3" s="310" t="inlineStr">
         <is>
           <t>SS16</t>
         </is>
       </c>
-      <c r="C3" s="303" t="n">
+      <c r="C3" s="310" t="n">
         <v>1440</v>
       </c>
       <c r="D3" s="85" t="n">
         <v>1485</v>
       </c>
-      <c r="E3" s="303" t="n">
+      <c r="E3" s="310" t="n">
         <v>20</v>
       </c>
-      <c r="F3" s="303" t="n"/>
+      <c r="F3" s="310" t="n"/>
       <c r="G3" s="243">
         <f>E3-F3</f>
         <v/>
@@ -2716,7 +2716,7 @@
           <t>16cut/Jet Black AB/SS16/Hot/002+</t>
         </is>
       </c>
-      <c r="I3" s="319" t="inlineStr">
+      <c r="I3" s="316" t="inlineStr">
         <is>
           <t>002+</t>
         </is>
@@ -2724,22 +2724,22 @@
     </row>
     <row r="4" ht="16.5" customHeight="1" thickBot="1" thickTop="1">
       <c r="A4" s="428" t="n"/>
-      <c r="B4" s="301" t="inlineStr">
+      <c r="B4" s="311" t="inlineStr">
         <is>
           <t>SS20</t>
         </is>
       </c>
-      <c r="C4" s="301" t="n">
+      <c r="C4" s="311" t="n">
         <v>1440</v>
       </c>
       <c r="D4" s="86" t="n">
         <v>1972</v>
       </c>
-      <c r="E4" s="301">
+      <c r="E4" s="311">
         <f>15+8-3</f>
         <v/>
       </c>
-      <c r="F4" s="301" t="n"/>
+      <c r="F4" s="311" t="n"/>
       <c r="G4" s="245">
         <f>E4-F4</f>
         <v/>
@@ -2753,21 +2753,21 @@
     </row>
     <row r="5" ht="16.5" customHeight="1" thickBot="1" thickTop="1">
       <c r="A5" s="430" t="n"/>
-      <c r="B5" s="302" t="inlineStr">
+      <c r="B5" s="312" t="inlineStr">
         <is>
           <t>SS30</t>
         </is>
       </c>
-      <c r="C5" s="302" t="n">
+      <c r="C5" s="312" t="n">
         <v>288</v>
       </c>
       <c r="D5" s="88" t="n">
         <v>1485</v>
       </c>
-      <c r="E5" s="302" t="n">
+      <c r="E5" s="312" t="n">
         <v>20</v>
       </c>
-      <c r="F5" s="302" t="n"/>
+      <c r="F5" s="312" t="n"/>
       <c r="G5" s="246">
         <f>E5-F5</f>
         <v/>
@@ -2780,26 +2780,26 @@
       <c r="I5" s="431" t="n"/>
     </row>
     <row r="6" ht="16.5" customHeight="1" thickBot="1" thickTop="1">
-      <c r="A6" s="317" t="inlineStr">
+      <c r="A6" s="319" t="inlineStr">
         <is>
           <t>TOPAZ AB</t>
         </is>
       </c>
-      <c r="B6" s="317" t="inlineStr">
+      <c r="B6" s="319" t="inlineStr">
         <is>
           <t>SS16</t>
         </is>
       </c>
-      <c r="C6" s="317" t="n">
+      <c r="C6" s="319" t="n">
         <v>1440</v>
       </c>
       <c r="D6" s="140" t="n">
         <v>1647</v>
       </c>
-      <c r="E6" s="317" t="n">
+      <c r="E6" s="319" t="n">
         <v>20</v>
       </c>
-      <c r="F6" s="317" t="n"/>
+      <c r="F6" s="319" t="n"/>
       <c r="G6" s="244">
         <f>E6-F6</f>
         <v/>
@@ -2809,7 +2809,7 @@
           <t>16cut/Topaz AB/SS16/Hot/008+</t>
         </is>
       </c>
-      <c r="I6" s="319" t="inlineStr">
+      <c r="I6" s="316" t="inlineStr">
         <is>
           <t>008+</t>
         </is>
@@ -2817,22 +2817,22 @@
     </row>
     <row r="7" ht="16.5" customHeight="1" thickBot="1" thickTop="1">
       <c r="A7" s="428" t="n"/>
-      <c r="B7" s="301" t="inlineStr">
+      <c r="B7" s="311" t="inlineStr">
         <is>
           <t>SS20</t>
         </is>
       </c>
-      <c r="C7" s="301" t="n">
+      <c r="C7" s="311" t="n">
         <v>1440</v>
       </c>
       <c r="D7" s="86" t="n">
         <v>2133</v>
       </c>
-      <c r="E7" s="301">
+      <c r="E7" s="311">
         <f>5+15</f>
         <v/>
       </c>
-      <c r="F7" s="301" t="n"/>
+      <c r="F7" s="311" t="n"/>
       <c r="G7" s="245">
         <f>E7-F7</f>
         <v/>
@@ -2846,21 +2846,21 @@
     </row>
     <row r="8" ht="16.5" customHeight="1" thickBot="1" thickTop="1">
       <c r="A8" s="430" t="n"/>
-      <c r="B8" s="318" t="inlineStr">
+      <c r="B8" s="320" t="inlineStr">
         <is>
           <t>SS30</t>
         </is>
       </c>
-      <c r="C8" s="318" t="n">
+      <c r="C8" s="320" t="n">
         <v>288</v>
       </c>
       <c r="D8" s="87" t="n">
         <v>1647</v>
       </c>
-      <c r="E8" s="318" t="n">
+      <c r="E8" s="320" t="n">
         <v>20</v>
       </c>
-      <c r="F8" s="318" t="n"/>
+      <c r="F8" s="320" t="n"/>
       <c r="G8" s="246">
         <f>E8-F8</f>
         <v/>
@@ -2873,26 +2873,26 @@
       <c r="I8" s="431" t="n"/>
     </row>
     <row r="9" ht="16.5" customHeight="1" thickBot="1" thickTop="1">
-      <c r="A9" s="303" t="inlineStr">
+      <c r="A9" s="310" t="inlineStr">
         <is>
           <t>Lt. Sapphire AB</t>
         </is>
       </c>
-      <c r="B9" s="303" t="inlineStr">
+      <c r="B9" s="310" t="inlineStr">
         <is>
           <t>SS16</t>
         </is>
       </c>
-      <c r="C9" s="303" t="n">
+      <c r="C9" s="310" t="n">
         <v>1440</v>
       </c>
       <c r="D9" s="85" t="n">
         <v>1647</v>
       </c>
-      <c r="E9" s="338" t="n">
+      <c r="E9" s="329" t="n">
         <v>20</v>
       </c>
-      <c r="F9" s="303">
+      <c r="F9" s="310">
         <f>1+1</f>
         <v/>
       </c>
@@ -2905,7 +2905,7 @@
           <t>16cut/Lt.Sapphire AB/SS16/Hot/011+</t>
         </is>
       </c>
-      <c r="I9" s="319" t="inlineStr">
+      <c r="I9" s="316" t="inlineStr">
         <is>
           <t>011+</t>
         </is>
@@ -2913,22 +2913,22 @@
     </row>
     <row r="10" ht="16.5" customHeight="1" thickBot="1" thickTop="1">
       <c r="A10" s="428" t="n"/>
-      <c r="B10" s="301" t="inlineStr">
+      <c r="B10" s="311" t="inlineStr">
         <is>
           <t>SS20</t>
         </is>
       </c>
-      <c r="C10" s="301" t="n">
+      <c r="C10" s="311" t="n">
         <v>1440</v>
       </c>
       <c r="D10" s="86" t="n">
         <v>2133</v>
       </c>
-      <c r="E10" s="336">
+      <c r="E10" s="330">
         <f>5+15</f>
         <v/>
       </c>
-      <c r="F10" s="301" t="n">
+      <c r="F10" s="311" t="n">
         <v>1</v>
       </c>
       <c r="G10" s="245">
@@ -2944,21 +2944,21 @@
     </row>
     <row r="11" ht="16.5" customHeight="1" thickBot="1" thickTop="1">
       <c r="A11" s="430" t="n"/>
-      <c r="B11" s="302" t="inlineStr">
+      <c r="B11" s="312" t="inlineStr">
         <is>
           <t>SS30</t>
         </is>
       </c>
-      <c r="C11" s="302" t="n">
+      <c r="C11" s="312" t="n">
         <v>288</v>
       </c>
       <c r="D11" s="88" t="n">
         <v>1647</v>
       </c>
-      <c r="E11" s="339" t="n">
+      <c r="E11" s="331" t="n">
         <v>20</v>
       </c>
-      <c r="F11" s="302" t="n">
+      <c r="F11" s="312" t="n">
         <v>1</v>
       </c>
       <c r="G11" s="246">
@@ -2973,26 +2973,26 @@
       <c r="I11" s="431" t="n"/>
     </row>
     <row r="12" ht="16.5" customHeight="1" thickBot="1" thickTop="1">
-      <c r="A12" s="317" t="inlineStr">
+      <c r="A12" s="319" t="inlineStr">
         <is>
           <t>INDICOLITE AB</t>
         </is>
       </c>
-      <c r="B12" s="317" t="inlineStr">
+      <c r="B12" s="319" t="inlineStr">
         <is>
           <t>SS16</t>
         </is>
       </c>
-      <c r="C12" s="317" t="n">
+      <c r="C12" s="319" t="n">
         <v>1440</v>
       </c>
       <c r="D12" s="140" t="n">
         <v>1647</v>
       </c>
-      <c r="E12" s="335" t="n">
+      <c r="E12" s="346" t="n">
         <v>20</v>
       </c>
-      <c r="F12" s="317" t="n"/>
+      <c r="F12" s="319" t="n"/>
       <c r="G12" s="244">
         <f>E12-F12</f>
         <v/>
@@ -3002,7 +3002,7 @@
           <t>16cut/Indicolite AB/SS16/Hot/014+</t>
         </is>
       </c>
-      <c r="I12" s="319" t="inlineStr">
+      <c r="I12" s="316" t="inlineStr">
         <is>
           <t>014+</t>
         </is>
@@ -3010,22 +3010,22 @@
     </row>
     <row r="13" ht="16.5" customHeight="1" thickBot="1" thickTop="1">
       <c r="A13" s="428" t="n"/>
-      <c r="B13" s="301" t="inlineStr">
+      <c r="B13" s="311" t="inlineStr">
         <is>
           <t>SS20</t>
         </is>
       </c>
-      <c r="C13" s="301" t="n">
+      <c r="C13" s="311" t="n">
         <v>1440</v>
       </c>
       <c r="D13" s="86" t="n">
         <v>2133</v>
       </c>
-      <c r="E13" s="336">
+      <c r="E13" s="330">
         <f>5+15</f>
         <v/>
       </c>
-      <c r="F13" s="301" t="n"/>
+      <c r="F13" s="311" t="n"/>
       <c r="G13" s="245">
         <f>E13-F13</f>
         <v/>
@@ -3039,21 +3039,21 @@
     </row>
     <row r="14" ht="16.5" customHeight="1" thickBot="1" thickTop="1">
       <c r="A14" s="430" t="n"/>
-      <c r="B14" s="318" t="inlineStr">
+      <c r="B14" s="320" t="inlineStr">
         <is>
           <t>SS30</t>
         </is>
       </c>
-      <c r="C14" s="318" t="n">
+      <c r="C14" s="320" t="n">
         <v>288</v>
       </c>
       <c r="D14" s="87" t="n">
         <v>1647</v>
       </c>
-      <c r="E14" s="337" t="n">
+      <c r="E14" s="347" t="n">
         <v>20</v>
       </c>
-      <c r="F14" s="318" t="n"/>
+      <c r="F14" s="320" t="n"/>
       <c r="G14" s="246">
         <f>E14-F14</f>
         <v/>
@@ -3066,26 +3066,26 @@
       <c r="I14" s="431" t="n"/>
     </row>
     <row r="15" ht="16.5" customHeight="1" thickBot="1" thickTop="1">
-      <c r="A15" s="303" t="inlineStr">
+      <c r="A15" s="310" t="inlineStr">
         <is>
           <t>AQUAMARINE AB</t>
         </is>
       </c>
-      <c r="B15" s="303" t="inlineStr">
+      <c r="B15" s="310" t="inlineStr">
         <is>
           <t>SS16</t>
         </is>
       </c>
-      <c r="C15" s="303" t="n">
+      <c r="C15" s="310" t="n">
         <v>1440</v>
       </c>
       <c r="D15" s="85" t="n">
         <v>1252</v>
       </c>
-      <c r="E15" s="338" t="n">
+      <c r="E15" s="329" t="n">
         <v>20</v>
       </c>
-      <c r="F15" s="303" t="n">
+      <c r="F15" s="310" t="n">
         <v>1</v>
       </c>
       <c r="G15" s="244">
@@ -3097,7 +3097,7 @@
           <t>16cut/Aquamarine AB/SS16/Hot/016+</t>
         </is>
       </c>
-      <c r="I15" s="319" t="inlineStr">
+      <c r="I15" s="316" t="inlineStr">
         <is>
           <t>016+</t>
         </is>
@@ -3105,22 +3105,22 @@
     </row>
     <row r="16" ht="16.5" customHeight="1" thickBot="1" thickTop="1">
       <c r="A16" s="428" t="n"/>
-      <c r="B16" s="301" t="inlineStr">
+      <c r="B16" s="311" t="inlineStr">
         <is>
           <t>SS20</t>
         </is>
       </c>
-      <c r="C16" s="301" t="n">
+      <c r="C16" s="311" t="n">
         <v>1440</v>
       </c>
       <c r="D16" s="86" t="n">
         <v>1858</v>
       </c>
-      <c r="E16" s="336">
+      <c r="E16" s="330">
         <f>5+15</f>
         <v/>
       </c>
-      <c r="F16" s="301" t="n"/>
+      <c r="F16" s="311" t="n"/>
       <c r="G16" s="245">
         <f>E16-F16</f>
         <v/>
@@ -3134,21 +3134,21 @@
     </row>
     <row r="17" ht="16.5" customHeight="1" thickBot="1" thickTop="1">
       <c r="A17" s="430" t="n"/>
-      <c r="B17" s="302" t="inlineStr">
+      <c r="B17" s="312" t="inlineStr">
         <is>
           <t>SS30</t>
         </is>
       </c>
-      <c r="C17" s="302" t="n">
+      <c r="C17" s="312" t="n">
         <v>288</v>
       </c>
       <c r="D17" s="88" t="n">
         <v>1252</v>
       </c>
-      <c r="E17" s="339" t="n">
+      <c r="E17" s="331" t="n">
         <v>20</v>
       </c>
-      <c r="F17" s="302" t="n"/>
+      <c r="F17" s="312" t="n"/>
       <c r="G17" s="246">
         <f>E17-F17</f>
         <v/>
@@ -3161,26 +3161,26 @@
       <c r="I17" s="431" t="n"/>
     </row>
     <row r="18" ht="16.5" customHeight="1" thickBot="1" thickTop="1">
-      <c r="A18" s="317" t="inlineStr">
+      <c r="A18" s="319" t="inlineStr">
         <is>
           <t>BLUE ZIRCON AB</t>
         </is>
       </c>
-      <c r="B18" s="317" t="inlineStr">
+      <c r="B18" s="319" t="inlineStr">
         <is>
           <t>SS16</t>
         </is>
       </c>
-      <c r="C18" s="317" t="n">
+      <c r="C18" s="319" t="n">
         <v>1440</v>
       </c>
       <c r="D18" s="140" t="n">
         <v>1647</v>
       </c>
-      <c r="E18" s="335" t="n">
+      <c r="E18" s="346" t="n">
         <v>20</v>
       </c>
-      <c r="F18" s="317" t="n">
+      <c r="F18" s="319" t="n">
         <v>1</v>
       </c>
       <c r="G18" s="244">
@@ -3192,7 +3192,7 @@
           <t>16cut/Blue Zircon AB/SS16/Hot/015+</t>
         </is>
       </c>
-      <c r="I18" s="319" t="inlineStr">
+      <c r="I18" s="316" t="inlineStr">
         <is>
           <t>015+</t>
         </is>
@@ -3200,22 +3200,22 @@
     </row>
     <row r="19" ht="16.5" customHeight="1" thickBot="1" thickTop="1">
       <c r="A19" s="428" t="n"/>
-      <c r="B19" s="301" t="inlineStr">
+      <c r="B19" s="311" t="inlineStr">
         <is>
           <t>SS20</t>
         </is>
       </c>
-      <c r="C19" s="301" t="n">
+      <c r="C19" s="311" t="n">
         <v>1440</v>
       </c>
       <c r="D19" s="86" t="n">
         <v>2133</v>
       </c>
-      <c r="E19" s="336">
+      <c r="E19" s="330">
         <f>5+15</f>
         <v/>
       </c>
-      <c r="F19" s="301" t="n"/>
+      <c r="F19" s="311" t="n"/>
       <c r="G19" s="245">
         <f>E19-F19</f>
         <v/>
@@ -3229,21 +3229,21 @@
     </row>
     <row r="20" ht="16.5" customHeight="1" thickBot="1" thickTop="1">
       <c r="A20" s="430" t="n"/>
-      <c r="B20" s="318" t="inlineStr">
+      <c r="B20" s="320" t="inlineStr">
         <is>
           <t>SS30</t>
         </is>
       </c>
-      <c r="C20" s="318" t="n">
+      <c r="C20" s="320" t="n">
         <v>288</v>
       </c>
       <c r="D20" s="87" t="n">
         <v>1647</v>
       </c>
-      <c r="E20" s="337" t="n">
+      <c r="E20" s="347" t="n">
         <v>20</v>
       </c>
-      <c r="F20" s="318" t="n"/>
+      <c r="F20" s="320" t="n"/>
       <c r="G20" s="246">
         <f>E20-F20</f>
         <v/>
@@ -3256,26 +3256,26 @@
       <c r="I20" s="431" t="n"/>
     </row>
     <row r="21" ht="16.5" customHeight="1" thickBot="1" thickTop="1">
-      <c r="A21" s="303" t="inlineStr">
+      <c r="A21" s="310" t="inlineStr">
         <is>
           <t>CAPRI BLUE AB</t>
         </is>
       </c>
-      <c r="B21" s="303" t="inlineStr">
+      <c r="B21" s="310" t="inlineStr">
         <is>
           <t>SS16</t>
         </is>
       </c>
-      <c r="C21" s="303" t="n">
+      <c r="C21" s="310" t="n">
         <v>1440</v>
       </c>
       <c r="D21" s="85" t="n">
         <v>1647</v>
       </c>
-      <c r="E21" s="338" t="n">
+      <c r="E21" s="329" t="n">
         <v>20</v>
       </c>
-      <c r="F21" s="303" t="n">
+      <c r="F21" s="310" t="n">
         <v>1</v>
       </c>
       <c r="G21" s="244">
@@ -3287,7 +3287,7 @@
           <t>16cut/Capri Blue AB/SS16/Hot/017+</t>
         </is>
       </c>
-      <c r="I21" s="319" t="inlineStr">
+      <c r="I21" s="316" t="inlineStr">
         <is>
           <t>017+</t>
         </is>
@@ -3295,22 +3295,22 @@
     </row>
     <row r="22" ht="16.5" customHeight="1" thickBot="1" thickTop="1">
       <c r="A22" s="428" t="n"/>
-      <c r="B22" s="301" t="inlineStr">
+      <c r="B22" s="311" t="inlineStr">
         <is>
           <t>SS20</t>
         </is>
       </c>
-      <c r="C22" s="301" t="n">
+      <c r="C22" s="311" t="n">
         <v>1440</v>
       </c>
       <c r="D22" s="86" t="n">
         <v>2133</v>
       </c>
-      <c r="E22" s="336">
+      <c r="E22" s="330">
         <f>5+15</f>
         <v/>
       </c>
-      <c r="F22" s="301" t="n">
+      <c r="F22" s="311" t="n">
         <v>1</v>
       </c>
       <c r="G22" s="245">
@@ -3326,21 +3326,21 @@
     </row>
     <row r="23" ht="16.5" customHeight="1" thickBot="1" thickTop="1">
       <c r="A23" s="430" t="n"/>
-      <c r="B23" s="302" t="inlineStr">
+      <c r="B23" s="312" t="inlineStr">
         <is>
           <t>SS30</t>
         </is>
       </c>
-      <c r="C23" s="302" t="n">
+      <c r="C23" s="312" t="n">
         <v>288</v>
       </c>
       <c r="D23" s="88" t="n">
         <v>1647</v>
       </c>
-      <c r="E23" s="339" t="n">
+      <c r="E23" s="331" t="n">
         <v>20</v>
       </c>
-      <c r="F23" s="302" t="n"/>
+      <c r="F23" s="312" t="n"/>
       <c r="G23" s="246">
         <f>E23-F23</f>
         <v/>
@@ -3353,26 +3353,26 @@
       <c r="I23" s="431" t="n"/>
     </row>
     <row r="24" ht="16.5" customHeight="1" thickBot="1" thickTop="1">
-      <c r="A24" s="317" t="inlineStr">
+      <c r="A24" s="319" t="inlineStr">
         <is>
           <t>OLIVINE AB</t>
         </is>
       </c>
-      <c r="B24" s="317" t="inlineStr">
+      <c r="B24" s="319" t="inlineStr">
         <is>
           <t>SS16</t>
         </is>
       </c>
-      <c r="C24" s="317" t="n">
+      <c r="C24" s="319" t="n">
         <v>1440</v>
       </c>
       <c r="D24" s="140" t="n">
         <v>1647</v>
       </c>
-      <c r="E24" s="335" t="n">
+      <c r="E24" s="346" t="n">
         <v>20</v>
       </c>
-      <c r="F24" s="317" t="n"/>
+      <c r="F24" s="319" t="n"/>
       <c r="G24" s="244">
         <f>E24-F24</f>
         <v/>
@@ -3382,7 +3382,7 @@
           <t>16cut/Olivine AB/SS16/Hot/027+</t>
         </is>
       </c>
-      <c r="I24" s="319" t="inlineStr">
+      <c r="I24" s="316" t="inlineStr">
         <is>
           <t>027+</t>
         </is>
@@ -3390,22 +3390,22 @@
     </row>
     <row r="25" ht="16.5" customHeight="1" thickBot="1" thickTop="1">
       <c r="A25" s="428" t="n"/>
-      <c r="B25" s="301" t="inlineStr">
+      <c r="B25" s="311" t="inlineStr">
         <is>
           <t>SS20</t>
         </is>
       </c>
-      <c r="C25" s="301" t="n">
+      <c r="C25" s="311" t="n">
         <v>1440</v>
       </c>
       <c r="D25" s="86" t="n">
         <v>2133</v>
       </c>
-      <c r="E25" s="336">
+      <c r="E25" s="330">
         <f>5+15</f>
         <v/>
       </c>
-      <c r="F25" s="301" t="n"/>
+      <c r="F25" s="311" t="n"/>
       <c r="G25" s="245">
         <f>E25-F25</f>
         <v/>
@@ -3419,21 +3419,21 @@
     </row>
     <row r="26" ht="16.5" customHeight="1" thickBot="1" thickTop="1">
       <c r="A26" s="430" t="n"/>
-      <c r="B26" s="318" t="inlineStr">
+      <c r="B26" s="320" t="inlineStr">
         <is>
           <t>SS30</t>
         </is>
       </c>
-      <c r="C26" s="318" t="n">
+      <c r="C26" s="320" t="n">
         <v>288</v>
       </c>
       <c r="D26" s="87" t="n">
         <v>1647</v>
       </c>
-      <c r="E26" s="337" t="n">
+      <c r="E26" s="347" t="n">
         <v>20</v>
       </c>
-      <c r="F26" s="318" t="n"/>
+      <c r="F26" s="320" t="n"/>
       <c r="G26" s="246">
         <f>E26-F26</f>
         <v/>
@@ -3446,26 +3446,26 @@
       <c r="I26" s="431" t="n"/>
     </row>
     <row r="27" ht="16.5" customHeight="1" thickBot="1" thickTop="1">
-      <c r="A27" s="303" t="inlineStr">
+      <c r="A27" s="310" t="inlineStr">
         <is>
           <t>HYACINTH AB</t>
         </is>
       </c>
-      <c r="B27" s="303" t="inlineStr">
+      <c r="B27" s="310" t="inlineStr">
         <is>
           <t>SS16</t>
         </is>
       </c>
-      <c r="C27" s="303" t="n">
+      <c r="C27" s="310" t="n">
         <v>1440</v>
       </c>
       <c r="D27" s="85" t="n">
         <v>1679</v>
       </c>
-      <c r="E27" s="338" t="n">
+      <c r="E27" s="329" t="n">
         <v>20</v>
       </c>
-      <c r="F27" s="303" t="n"/>
+      <c r="F27" s="310" t="n"/>
       <c r="G27" s="244">
         <f>E27-F27</f>
         <v/>
@@ -3475,7 +3475,7 @@
           <t>16cut/Hyacinth AB/SS16/Hot/031+</t>
         </is>
       </c>
-      <c r="I27" s="319" t="inlineStr">
+      <c r="I27" s="316" t="inlineStr">
         <is>
           <t>031+</t>
         </is>
@@ -3483,22 +3483,22 @@
     </row>
     <row r="28" ht="16.5" customHeight="1" thickBot="1" thickTop="1">
       <c r="A28" s="428" t="n"/>
-      <c r="B28" s="301" t="inlineStr">
+      <c r="B28" s="311" t="inlineStr">
         <is>
           <t>SS20</t>
         </is>
       </c>
-      <c r="C28" s="301" t="n">
+      <c r="C28" s="311" t="n">
         <v>1440</v>
       </c>
       <c r="D28" s="86" t="n">
         <v>2166</v>
       </c>
-      <c r="E28" s="336">
+      <c r="E28" s="330">
         <f>5+15</f>
         <v/>
       </c>
-      <c r="F28" s="301" t="n"/>
+      <c r="F28" s="311" t="n"/>
       <c r="G28" s="245">
         <f>E28-F28</f>
         <v/>
@@ -3512,21 +3512,21 @@
     </row>
     <row r="29" ht="16.5" customHeight="1" thickBot="1" thickTop="1">
       <c r="A29" s="430" t="n"/>
-      <c r="B29" s="302" t="inlineStr">
+      <c r="B29" s="312" t="inlineStr">
         <is>
           <t>SS30</t>
         </is>
       </c>
-      <c r="C29" s="302" t="n">
+      <c r="C29" s="312" t="n">
         <v>288</v>
       </c>
       <c r="D29" s="88" t="n">
         <v>1679</v>
       </c>
-      <c r="E29" s="339" t="n">
+      <c r="E29" s="331" t="n">
         <v>20</v>
       </c>
-      <c r="F29" s="302" t="n"/>
+      <c r="F29" s="312" t="n"/>
       <c r="G29" s="246">
         <f>E29-F29</f>
         <v/>
@@ -3539,26 +3539,26 @@
       <c r="I29" s="431" t="n"/>
     </row>
     <row r="30" ht="16.5" customHeight="1" thickBot="1" thickTop="1">
-      <c r="A30" s="317" t="inlineStr">
+      <c r="A30" s="319" t="inlineStr">
         <is>
           <t>Lt. Siam AB</t>
         </is>
       </c>
-      <c r="B30" s="317" t="inlineStr">
+      <c r="B30" s="319" t="inlineStr">
         <is>
           <t>SS16</t>
         </is>
       </c>
-      <c r="C30" s="317" t="n">
+      <c r="C30" s="319" t="n">
         <v>1440</v>
       </c>
       <c r="D30" s="140" t="n">
         <v>1809</v>
       </c>
-      <c r="E30" s="335" t="n">
+      <c r="E30" s="346" t="n">
         <v>20</v>
       </c>
-      <c r="F30" s="317" t="n">
+      <c r="F30" s="319" t="n">
         <v>1</v>
       </c>
       <c r="G30" s="244">
@@ -3570,7 +3570,7 @@
           <t>16cut/Lt.Siam AB/SS16/Hot/039+</t>
         </is>
       </c>
-      <c r="I30" s="320" t="inlineStr">
+      <c r="I30" s="317" t="inlineStr">
         <is>
           <t>039+</t>
         </is>
@@ -3578,21 +3578,21 @@
     </row>
     <row r="31" ht="16.5" customHeight="1" thickBot="1" thickTop="1">
       <c r="A31" s="428" t="n"/>
-      <c r="B31" s="301" t="inlineStr">
+      <c r="B31" s="311" t="inlineStr">
         <is>
           <t>SS20</t>
         </is>
       </c>
-      <c r="C31" s="301" t="n">
+      <c r="C31" s="311" t="n">
         <v>1440</v>
       </c>
       <c r="D31" s="86" t="n">
         <v>2133</v>
       </c>
-      <c r="E31" s="336" t="n">
+      <c r="E31" s="330" t="n">
         <v>20</v>
       </c>
-      <c r="F31" s="301" t="n">
+      <c r="F31" s="311" t="n">
         <v>1</v>
       </c>
       <c r="G31" s="245">
@@ -3608,21 +3608,21 @@
     </row>
     <row r="32" ht="16.5" customHeight="1" thickBot="1" thickTop="1">
       <c r="A32" s="430" t="n"/>
-      <c r="B32" s="318" t="inlineStr">
+      <c r="B32" s="320" t="inlineStr">
         <is>
           <t>SS30</t>
         </is>
       </c>
-      <c r="C32" s="318" t="n">
+      <c r="C32" s="320" t="n">
         <v>288</v>
       </c>
       <c r="D32" s="87" t="n">
         <v>1809</v>
       </c>
-      <c r="E32" s="337" t="n">
+      <c r="E32" s="347" t="n">
         <v>20</v>
       </c>
-      <c r="F32" s="318" t="n">
+      <c r="F32" s="320" t="n">
         <v>1</v>
       </c>
       <c r="G32" s="246">
@@ -3637,26 +3637,26 @@
       <c r="I32" s="431" t="n"/>
     </row>
     <row r="33" ht="16.5" customHeight="1" thickBot="1" thickTop="1">
-      <c r="A33" s="303" t="inlineStr">
+      <c r="A33" s="310" t="inlineStr">
         <is>
           <t>CITRINE AB</t>
         </is>
       </c>
-      <c r="B33" s="303" t="inlineStr">
+      <c r="B33" s="310" t="inlineStr">
         <is>
           <t>SS16</t>
         </is>
       </c>
-      <c r="C33" s="303" t="n">
+      <c r="C33" s="310" t="n">
         <v>1440</v>
       </c>
       <c r="D33" s="85" t="n">
         <v>1809</v>
       </c>
-      <c r="E33" s="338" t="n">
+      <c r="E33" s="329" t="n">
         <v>20</v>
       </c>
-      <c r="F33" s="303" t="n">
+      <c r="F33" s="310" t="n">
         <v>1</v>
       </c>
       <c r="G33" s="244">
@@ -3668,7 +3668,7 @@
           <t>16cut/Citrine AB/SS16/Hot/035+</t>
         </is>
       </c>
-      <c r="I33" s="319" t="inlineStr">
+      <c r="I33" s="316" t="inlineStr">
         <is>
           <t>035+</t>
         </is>
@@ -3676,22 +3676,22 @@
     </row>
     <row r="34" ht="16.5" customHeight="1" thickBot="1" thickTop="1">
       <c r="A34" s="428" t="n"/>
-      <c r="B34" s="301" t="inlineStr">
+      <c r="B34" s="311" t="inlineStr">
         <is>
           <t>SS20</t>
         </is>
       </c>
-      <c r="C34" s="301" t="n">
+      <c r="C34" s="311" t="n">
         <v>1440</v>
       </c>
       <c r="D34" s="86" t="n">
         <v>2133</v>
       </c>
-      <c r="E34" s="301">
+      <c r="E34" s="311">
         <f>15+5</f>
         <v/>
       </c>
-      <c r="F34" s="301" t="n"/>
+      <c r="F34" s="311" t="n"/>
       <c r="G34" s="245">
         <f>E34-F34</f>
         <v/>
@@ -3705,21 +3705,21 @@
     </row>
     <row r="35" ht="16.5" customHeight="1" thickBot="1" thickTop="1">
       <c r="A35" s="430" t="n"/>
-      <c r="B35" s="302" t="inlineStr">
+      <c r="B35" s="312" t="inlineStr">
         <is>
           <t>SS30</t>
         </is>
       </c>
-      <c r="C35" s="302" t="n">
+      <c r="C35" s="312" t="n">
         <v>288</v>
       </c>
       <c r="D35" s="88" t="n">
         <v>1809</v>
       </c>
-      <c r="E35" s="339" t="n">
+      <c r="E35" s="331" t="n">
         <v>20</v>
       </c>
-      <c r="F35" s="302" t="n"/>
+      <c r="F35" s="312" t="n"/>
       <c r="G35" s="246">
         <f>E35-F35</f>
         <v/>
@@ -3734,29 +3734,29 @@
     <row r="36" ht="15.75" customHeight="1" thickTop="1"/>
   </sheetData>
   <mergeCells count="23">
+    <mergeCell ref="A21:A23"/>
     <mergeCell ref="I18:I20"/>
-    <mergeCell ref="A21:A23"/>
     <mergeCell ref="A12:A14"/>
     <mergeCell ref="A33:A35"/>
     <mergeCell ref="I6:I8"/>
     <mergeCell ref="A15:A17"/>
-    <mergeCell ref="I24:I26"/>
+    <mergeCell ref="A24:A26"/>
     <mergeCell ref="I15:I17"/>
-    <mergeCell ref="A24:A26"/>
     <mergeCell ref="I9:I11"/>
     <mergeCell ref="A9:A11"/>
     <mergeCell ref="I27:I29"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A30:A32"/>
     <mergeCell ref="I30:I32"/>
+    <mergeCell ref="I3:I5"/>
     <mergeCell ref="A6:A8"/>
-    <mergeCell ref="I3:I5"/>
+    <mergeCell ref="A3:A5"/>
     <mergeCell ref="I12:I14"/>
-    <mergeCell ref="A3:A5"/>
+    <mergeCell ref="A27:A29"/>
     <mergeCell ref="I21:I23"/>
     <mergeCell ref="I33:I35"/>
     <mergeCell ref="A18:A20"/>
-    <mergeCell ref="A27:A29"/>
+    <mergeCell ref="I24:I26"/>
   </mergeCells>
   <pageMargins left="0.7086614173228347" right="0.7086614173228347" top="0.7480314960629921" bottom="0.7480314960629921" header="0.3149606299212598" footer="0.3149606299212598"/>
   <pageSetup orientation="portrait" paperSize="9" scale="92" verticalDpi="0"/>
